--- a/data/trans_dic/P34B01_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P34B01_R-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más</t>
+          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,47; 49,49</t>
+          <t>41,52; 49,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,63; 59,18</t>
+          <t>51,6; 59,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,53; 66,31</t>
+          <t>56,99; 65,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,49; 60,36</t>
+          <t>52,57; 60,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,94; 59,62</t>
+          <t>51,66; 59,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,19; 67,04</t>
+          <t>61,1; 66,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,12; 53,66</t>
+          <t>48,15; 53,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52,47; 58,11</t>
+          <t>52,72; 58,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,15; 65,5</t>
+          <t>60,26; 65,55</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,1; 46,49</t>
+          <t>40,24; 46,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,36; 51,84</t>
+          <t>45,1; 51,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,4; 63,11</t>
+          <t>24,28; 63,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,38; 47,4</t>
+          <t>41,46; 47,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,47; 50,12</t>
+          <t>43,55; 49,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,56; 65,77</t>
+          <t>60,41; 66,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,66; 46,15</t>
+          <t>41,62; 45,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,51; 49,94</t>
+          <t>45,45; 49,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,87; 63,23</t>
+          <t>36,02; 63,17</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45,05; 52,99</t>
+          <t>44,96; 52,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,45; 58,33</t>
+          <t>50,75; 58,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,58; 71,0</t>
+          <t>62,16; 70,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,59; 58,18</t>
+          <t>50,61; 58,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,48; 54,93</t>
+          <t>47,61; 54,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,76; 82,76</t>
+          <t>54,16; 82,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,78; 54,32</t>
+          <t>48,9; 54,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,24; 55,41</t>
+          <t>50,31; 55,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59,96; 78,07</t>
+          <t>60,07; 78,22</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,2; 44,81</t>
+          <t>38,34; 44,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,11; 62,32</t>
+          <t>55,9; 62,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,43; 70,34</t>
+          <t>63,78; 70,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,77; 48,79</t>
+          <t>42,81; 49,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,85; 63,02</t>
+          <t>56,72; 62,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,73; 61,73</t>
+          <t>46,33; 61,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,59; 46,1</t>
+          <t>41,56; 46,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,43; 61,88</t>
+          <t>57,25; 61,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,63; 64,88</t>
+          <t>54,37; 64,63</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,75; 46,36</t>
+          <t>42,7; 46,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,55; 55,84</t>
+          <t>52,44; 56,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,47; 65,07</t>
+          <t>45,4; 65,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,55; 51,04</t>
+          <t>47,76; 51,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,75; 55,08</t>
+          <t>51,57; 55,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,4; 68,48</t>
+          <t>58,54; 69,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,82; 48,31</t>
+          <t>45,71; 48,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>52,55; 55,02</t>
+          <t>52,46; 54,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52,94; 64,75</t>
+          <t>53,76; 64,56</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más</t>
+          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>291224; 347541</t>
+          <t>291570; 345364</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>348389; 399359</t>
+          <t>348228; 400211</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>363034; 418434</t>
+          <t>359626; 414847</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>365894; 420743</t>
+          <t>366407; 418850</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>349474; 401152</t>
+          <t>347579; 397687</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>410812; 450082</t>
+          <t>410230; 448593</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>673421; 750884</t>
+          <t>673722; 746859</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>707154; 783175</t>
+          <t>710491; 782350</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>783445; 853014</t>
+          <t>784807; 853714</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>408208; 473264</t>
+          <t>409597; 476154</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>463811; 530057</t>
+          <t>461112; 528772</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>324886; 748426</t>
+          <t>287990; 750339</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>426350; 488372</t>
+          <t>427136; 491367</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>453321; 522662</t>
+          <t>454232; 520065</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>577467; 627171</t>
+          <t>576052; 629950</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>853362; 945261</t>
+          <t>852511; 940885</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>940009; 1031402</t>
+          <t>938780; 1032413</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>767354; 1352851</t>
+          <t>770738; 1351586</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>341322; 401488</t>
+          <t>340627; 399329</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>383197; 443040</t>
+          <t>385472; 443066</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>439482; 498592</t>
+          <t>436472; 497639</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>393209; 452197</t>
+          <t>393354; 451784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>372761; 431183</t>
+          <t>373743; 431294</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>506708; 765827</t>
+          <t>501211; 767362</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>748628; 833665</t>
+          <t>750468; 833908</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>775984; 855891</t>
+          <t>777108; 855996</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>975871; 1270615</t>
+          <t>977760; 1273188</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>361688; 424315</t>
+          <t>363066; 422701</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>526056; 584261</t>
+          <t>524069; 585692</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>587820; 651850</t>
+          <t>591002; 653484</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>449891; 513238</t>
+          <t>450328; 516478</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>593414; 657839</t>
+          <t>592083; 655718</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>477142; 673553</t>
+          <t>505535; 674775</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>831334; 921363</t>
+          <t>830716; 924956</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1137943; 1226033</t>
+          <t>1134256; 1224889</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1102251; 1309253</t>
+          <t>1097159; 1304123</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1464067; 1587622</t>
+          <t>1462378; 1587521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1783825; 1895308</t>
+          <t>1779993; 1901186</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1566737; 2242151</t>
+          <t>1564500; 2246886</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1690974; 1815026</t>
+          <t>1698472; 1820255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1834306; 1952199</t>
+          <t>1827756; 1954278</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2126557; 2493674</t>
+          <t>2131832; 2518286</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3198768; 3372382</t>
+          <t>3190779; 3370581</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3646571; 3818082</t>
+          <t>3639807; 3809963</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3752286; 4588831</t>
+          <t>3810020; 4575706</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B01_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P34B01_R-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,0%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,52; 49,18</t>
+          <t>41,72; 49,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,6; 59,31</t>
+          <t>51,63; 59,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,99; 65,74</t>
+          <t>58,6; 66,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,57; 60,09</t>
+          <t>52,67; 60,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,66; 59,11</t>
+          <t>51,64; 59,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,1; 66,82</t>
+          <t>60,34; 66,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,15; 53,37</t>
+          <t>48,01; 53,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52,72; 58,05</t>
+          <t>53,02; 57,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,26; 65,55</t>
+          <t>60,54; 65,52</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>63,98%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,24; 46,78</t>
+          <t>40,23; 46,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,1; 51,72</t>
+          <t>45,3; 51,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,28; 63,27</t>
+          <t>60,48; 67,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,46; 47,69</t>
+          <t>41,04; 47,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,55; 49,87</t>
+          <t>43,59; 50,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,41; 66,06</t>
+          <t>61,6; 67,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,62; 45,94</t>
+          <t>41,69; 46,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,45; 49,99</t>
+          <t>45,41; 49,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,02; 63,17</t>
+          <t>61,8; 66,19</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,96; 52,71</t>
+          <t>45,04; 52,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,75; 58,33</t>
+          <t>50,91; 58,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,16; 70,87</t>
+          <t>62,56; 70,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,61; 58,13</t>
+          <t>50,73; 58,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,61; 54,94</t>
+          <t>47,62; 54,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,16; 82,92</t>
+          <t>57,08; 63,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,9; 54,33</t>
+          <t>49,06; 54,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,31; 55,42</t>
+          <t>50,39; 55,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60,07; 78,22</t>
+          <t>60,97; 65,97</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>64,7%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,34; 44,64</t>
+          <t>38,35; 45,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,9; 62,47</t>
+          <t>56,02; 62,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,78; 70,52</t>
+          <t>65,55; 71,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,81; 49,1</t>
+          <t>42,18; 48,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,72; 62,82</t>
+          <t>56,88; 63,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,33; 61,84</t>
+          <t>58,3; 63,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,56; 46,28</t>
+          <t>41,56; 45,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,25; 61,82</t>
+          <t>57,47; 62,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,37; 64,63</t>
+          <t>62,58; 66,79</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,7; 46,35</t>
+          <t>42,89; 46,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,44; 56,01</t>
+          <t>52,47; 55,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,4; 65,21</t>
+          <t>63,82; 67,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,76; 51,18</t>
+          <t>47,71; 51,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,57; 55,13</t>
+          <t>51,73; 55,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,54; 69,15</t>
+          <t>61,12; 63,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,71; 48,28</t>
+          <t>45,71; 48,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>52,46; 54,91</t>
+          <t>52,55; 54,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53,76; 64,56</t>
+          <t>62,7; 65,07</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>390591</t>
+          <t>429503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>429738</t>
+          <t>461690</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>820329</t>
+          <t>891193</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>291570; 345364</t>
+          <t>293002; 345911</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>348228; 400211</t>
+          <t>348368; 401261</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>359626; 414847</t>
+          <t>401948; 459349</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>366407; 418850</t>
+          <t>367129; 421013</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>347579; 397687</t>
+          <t>347459; 398332</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>410230; 448593</t>
+          <t>439646; 483415</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>673722; 746859</t>
+          <t>671883; 750575</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>710491; 782350</t>
+          <t>714476; 780682</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>784807; 853714</t>
+          <t>856407; 926834</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583852</t>
+          <t>662417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>602018</t>
+          <t>685744</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1185869</t>
+          <t>1348161</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>409597; 476154</t>
+          <t>409529; 477443</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>461112; 528772</t>
+          <t>463198; 529872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>287990; 750339</t>
+          <t>629616; 699028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>427136; 491367</t>
+          <t>422861; 487850</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>454232; 520065</t>
+          <t>454639; 521644</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>576052; 629950</t>
+          <t>656688; 714267</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>852511; 940885</t>
+          <t>853864; 947159</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>938780; 1032413</t>
+          <t>937791; 1030316</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>770738; 1351586</t>
+          <t>1302119; 1394703</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468621</t>
+          <t>534957</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>613642</t>
+          <t>486758</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1082262</t>
+          <t>1021715</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>340627; 399329</t>
+          <t>341230; 399967</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>385472; 443066</t>
+          <t>386670; 441138</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>436472; 497639</t>
+          <t>500730; 567553</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>393354; 451784</t>
+          <t>394269; 453009</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>373743; 431294</t>
+          <t>373799; 429959</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>501211; 767362</t>
+          <t>458987; 511698</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>750468; 833908</t>
+          <t>753023; 832292</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>777108; 855996</t>
+          <t>778249; 855481</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>977760; 1273188</t>
+          <t>978313; 1058507</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>621596</t>
+          <t>679013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>622405</t>
+          <t>683477</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1244001</t>
+          <t>1362490</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>363066; 422701</t>
+          <t>363133; 426333</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>524069; 585692</t>
+          <t>525234; 582136</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>591002; 653484</t>
+          <t>648270; 709953</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>450328; 516478</t>
+          <t>443723; 510622</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>592083; 655718</t>
+          <t>593729; 658482</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>505535; 674775</t>
+          <t>651110; 710654</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>830716; 924956</t>
+          <t>830596; 917135</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1134256; 1224889</t>
+          <t>1138654; 1228698</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1097159; 1304123</t>
+          <t>1317845; 1406436</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2064659</t>
+          <t>2305891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2267802</t>
+          <t>2317668</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4332462</t>
+          <t>4623559</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1462378; 1587521</t>
+          <t>1468850; 1586102</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1779993; 1901186</t>
+          <t>1781020; 1895981</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1564500; 2246886</t>
+          <t>2243971; 2369034</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1698472; 1820255</t>
+          <t>1696677; 1819503</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1827756; 1954278</t>
+          <t>1833690; 1954092</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2131832; 2518286</t>
+          <t>2270890; 2373455</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3190779; 3370581</t>
+          <t>3190897; 3376370</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3639807; 3809963</t>
+          <t>3646552; 3812051</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3810020; 4575706</t>
+          <t>4534560; 4706158</t>
         </is>
       </c>
     </row>
